--- a/apps/api/assets/vocabulary/初中/沪教版/沪教版牛津英语七年级下册.xlsx
+++ b/apps/api/assets/vocabulary/初中/沪教版/沪教版牛津英语七年级下册.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D233"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -937,6 +937,16 @@
           <t>take care of</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 照看；处理；清除
@@ -950,6 +960,16 @@
           <t>tell jokes</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 讲笑话；说笑话；讲个笑话</t>
@@ -962,6 +982,16 @@
           <t>make fun of</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 嘲弄
@@ -975,6 +1005,16 @@
           <t>strict about</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -987,6 +1027,16 @@
           <t>be strict about</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
           <t>对…严格</t>
@@ -999,6 +1049,16 @@
           <t>give up</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 放弃；断绝；投降；自首
@@ -1012,6 +1072,16 @@
           <t>go to work</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 着手工作
@@ -1023,6 +1093,16 @@
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>all day and all night</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1628,6 +1708,16 @@
           <t>famous for</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 以…著称
@@ -1641,6 +1731,16 @@
           <t>be famous for</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 因…出名
@@ -1654,6 +1754,16 @@
           <t>department store</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 百货公司；大百货商店
@@ -1667,6 +1777,16 @@
           <t>prefer to</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 较喜欢；宁愿:
@@ -1680,6 +1800,16 @@
           <t>go on holiday</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 去渡假
@@ -1691,6 +1821,16 @@
       <c r="A60" s="2" t="inlineStr">
         <is>
           <t>go sightseeing</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2256,6 +2396,16 @@
           <t>arrive at</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 到达；得出
@@ -2269,6 +2419,16 @@
           <t>by oneself</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 单独；独自；独力
@@ -2282,6 +2442,16 @@
           <t>lead to</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 通向
@@ -2295,6 +2465,16 @@
           <t>lead sb. to</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 通向
@@ -2308,6 +2488,16 @@
           <t>fall asleep</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 入睡
@@ -2342,6 +2532,16 @@
       <c r="A90" s="2" t="inlineStr">
         <is>
           <t>get down</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -2879,6 +3079,16 @@
           <t>take in</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 加以考虑；〔美国〕访问；收进；收容
@@ -2892,6 +3102,16 @@
           <t>come from</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 来自；出身；归因于
@@ -2928,6 +3148,16 @@
           <t>in fact</t>
         </is>
       </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 事实上；总之
@@ -2941,6 +3171,16 @@
           <t>look around</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 看起来好像；环视
@@ -2954,6 +3194,16 @@
           <t>made of</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. “make certain”的变体
@@ -2967,6 +3217,16 @@
           <t>be made of</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. …制的
@@ -2980,6 +3240,16 @@
           <t>millions of</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">det. 数百万
@@ -2993,6 +3263,16 @@
           <t>good for</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 擅长；拿手的；精明的；非常拿手的
@@ -3004,6 +3284,16 @@
       <c r="A122" s="2" t="inlineStr">
         <is>
           <t>be good for</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -3590,6 +3880,16 @@
           <t>add ... to ...</t>
         </is>
       </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 增加
@@ -3603,6 +3903,16 @@
           <t>a bit</t>
         </is>
       </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 有点儿〔作副词用〕
@@ -3616,6 +3926,16 @@
           <t>part of</t>
         </is>
       </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">adj. 部分
@@ -3629,6 +3949,16 @@
           <t>pocket money</t>
         </is>
       </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 零用钱；常用于英式英语
@@ -3642,6 +3972,16 @@
           <t>made up of</t>
         </is>
       </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 由…组成
@@ -3655,6 +3995,16 @@
           <t>be made up of</t>
         </is>
       </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 由…构成；组成；由…组成</t>
@@ -3665,6 +4015,16 @@
       <c r="A153" s="2" t="inlineStr">
         <is>
           <t>dry up</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -4127,6 +4487,16 @@
           <t>a packet of</t>
         </is>
       </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">det. 一包
@@ -4140,6 +4510,16 @@
           <t>in a way</t>
         </is>
       </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 在某一点上
@@ -4153,6 +4533,16 @@
           <t>connected to</t>
         </is>
       </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 连接到；接上一张；已连线到</t>
@@ -4165,6 +4555,16 @@
           <t>be connected to</t>
         </is>
       </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 与……相连接；被连接到；和…连在一起</t>
@@ -4177,6 +4577,16 @@
           <t>power station</t>
         </is>
       </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 发电厂；发电站
@@ -4190,6 +4600,16 @@
           <t>washing machine</t>
         </is>
       </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 洗衣机
@@ -4203,6 +4623,16 @@
           <t>switch off</t>
         </is>
       </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 不收听(某一广播)
@@ -4216,6 +4646,16 @@
           <t>tidy up</t>
         </is>
       </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 整理干净
@@ -4227,6 +4667,16 @@
       <c r="A181" s="2" t="inlineStr">
         <is>
           <t>air conditioner</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -4760,6 +5210,16 @@
           <t>not at all</t>
         </is>
       </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 毫无(=〔美国英语〕 You are welcome)
@@ -4773,6 +5233,16 @@
           <t>worried about</t>
         </is>
       </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 担心；对…担心；担心做某事</t>
@@ -4785,6 +5255,16 @@
           <t>be worried about</t>
         </is>
       </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 担心；为…而担心；为……担心</t>
@@ -4797,6 +5277,16 @@
           <t>newspaper stand</t>
         </is>
       </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 报摊
@@ -4810,6 +5300,16 @@
           <t>rush out</t>
         </is>
       </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 赶制出来
@@ -4821,6 +5321,16 @@
       <c r="A209" s="2" t="inlineStr">
         <is>
           <t>a crowd of</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -5235,6 +5745,16 @@
           <t>in the future</t>
         </is>
       </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">adv. 今后
@@ -5248,6 +5768,16 @@
           <t>used to</t>
         </is>
       </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">modalv. （用于过去持续或经常发生的事）曾经
@@ -5262,6 +5792,16 @@
           <t>go outside</t>
         </is>
       </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 到户外
@@ -5275,6 +5815,16 @@
           <t>look like</t>
         </is>
       </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 看起来与（某人或某物）相像[相似]; 很可能出现[引起]（某事、做某事）; 伣; 似</t>
@@ -5287,6 +5837,16 @@
           <t>more and more</t>
         </is>
       </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 越来越…
@@ -5321,6 +5881,16 @@
       <c r="A233" s="2" t="inlineStr">
         <is>
           <t>go sailing</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
